--- a/src/test/resources/InputData.xlsx
+++ b/src/test/resources/InputData.xlsx
@@ -1,48 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Automation_PFE\TestAutomation\src\test\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF562B4E-6C96-41C9-ADA9-FE2F1924BD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2964" yWindow="2964" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>testautosujet10</t>
-  </si>
-  <si>
-    <t>Azerty123!</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -72,21 +72,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -411,36 +403,118 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Password</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Count</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Street number and name</v>
+      </c>
+      <c r="E1" t="str">
+        <v>City</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Postal code</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Phone number</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Birth date</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Social security number</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Family member name</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Family member last name</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Family member address</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Family member phone number</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Family member mail</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Family member city</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Family member province</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Family member postal code</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>testautosujet10</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Azerty123!</v>
       </c>
       <c r="C2" t="n">
-        <v>19.0</v>
+        <v>118.0</v>
+      </c>
+      <c r="D2" t="str">
+        <v>123 test test</v>
+      </c>
+      <c r="E2" t="str">
+        <v>test</v>
+      </c>
+      <c r="F2" t="str">
+        <v>X1X1X1</v>
+      </c>
+      <c r="G2" t="str">
+        <v>(514) 555-5555</v>
+      </c>
+      <c r="H2" t="str">
+        <v>19880202</v>
+      </c>
+      <c r="I2" t="str">
+        <v>999 999 998</v>
+      </c>
+      <c r="J2" t="str">
+        <v>test</v>
+      </c>
+      <c r="K2" t="str">
+        <v>test</v>
+      </c>
+      <c r="L2" t="str">
+        <v>123 test test</v>
+      </c>
+      <c r="M2" t="str">
+        <v>(514) 555-5555</v>
+      </c>
+      <c r="N2" t="str">
+        <v>test@gmail.com</v>
+      </c>
+      <c r="O2" t="str">
+        <v>test</v>
+      </c>
+      <c r="P2" t="str">
+        <v>test</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>X1X1X1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C1 A2:B2" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q2"/>
   </ignoredErrors>
 </worksheet>
 </file>